--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="110">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:09:40+00:00</t>
+    <t>2023-06-08T09:23:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -341,30 +341,17 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Liste des conventionnement CNAM.</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J130-CNAMAmeliSecteurConventionnement-RASS/FHIR/JDV-J130-CNAMAmeliSecteurConventionnement-RASS</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Liste des conventionnement CNAM.</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J130-CNAMAmeliSecteurConventionnement-RASS/FHIR/JDV-J130-CNAMAmeliSecteurConventionnement-RASS</t>
   </si>
 </sst>
 </file>
@@ -666,12 +653,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK7"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.9765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="19.59765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="19.59765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1297,26 +1284,28 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AC6" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>102</v>
@@ -1331,114 +1320,9 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X7" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y7" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Z7" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AA7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK7" t="s" s="2">
         <v>101</v>
       </c>
     </row>
